--- a/excel_files/recently_deleted_employees.xlsx
+++ b/excel_files/recently_deleted_employees.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,21 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Sat</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Set Schedule</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Max Per Week</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Time Off Dates</t>
         </is>
       </c>
     </row>
